--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_o_higgins_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_o_higgins_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:18</t>
+    <t xml:space="preserve">2026-09-29 14:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_o_higgins_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_o_higgins_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:07</t>
+    <t xml:space="preserve">2026-09-29 18:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,7 +490,7 @@
         <v>13.31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>102.26</v>
+        <v>102.25</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>88.94</v>
@@ -504,7 +504,7 @@
         <v>9.1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>48.25</v>
+        <v>48.24</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>39.15</v>
@@ -521,7 +521,7 @@
         <v>37.55</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>33.79</v>
+        <v>33.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_o_higgins_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_o_higgins_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:45</t>
+    <t xml:space="preserve">2026-10-05 04:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,10 +490,10 @@
         <v>13.31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>102.25</v>
+        <v>102.26</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>88.94</v>
+        <v>88.95</v>
       </c>
     </row>
     <row r="3">
@@ -504,7 +504,7 @@
         <v>9.1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>48.24</v>
+        <v>48.25</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>39.15</v>
